--- a/data-manipulation-scripts/sheets-cleanup/sheets/BICO INJETOR - 30_01 A.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/BICO INJETOR - 30_01 A.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t>CÓD. BARRA</t>
   </si>
@@ -191,6 +191,9 @@
   </si>
   <si>
     <t>JUNCAO BICO INJETOR IRON CB/ XRE300 198651</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -552,7 +555,9 @@
       <c r="C6" s="2">
         <v>1.0</v>
       </c>
-      <c r="D6" s="3"/>
+      <c r="D6" s="2">
+        <v>120.0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
@@ -578,7 +583,9 @@
       <c r="C8" s="2">
         <v>2.0</v>
       </c>
-      <c r="D8" s="3"/>
+      <c r="D8" s="2">
+        <v>120.0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
@@ -856,7 +863,9 @@
       <c r="C28" s="2">
         <v>1.0</v>
       </c>
-      <c r="D28" s="3"/>
+      <c r="D28" s="2">
+        <v>130.0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
@@ -865,11 +874,17 @@
       <c r="B29" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
+      <c r="C29" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="D29" s="2">
+        <v>125.0</v>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="4"/>
+      <c r="A30" s="1" t="s">
+        <v>60</v>
+      </c>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
